--- a/Client/Tables/G_VerInfoTable.xlsx
+++ b/Client/Tables/G_VerInfoTable.xlsx
@@ -18,13 +18,13 @@
     <t>NOEX_Description</t>
   </si>
   <si>
-    <t>True_01</t>
+    <t>Flags_01</t>
   </si>
   <si>
-    <t>True_02</t>
+    <t>Flags_02</t>
   </si>
   <si>
-    <t>True_03</t>
+    <t>Flags_03</t>
   </si>
   <si>
     <t>Name</t>
@@ -140,7 +140,7 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="bottom"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -366,8 +366,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>
@@ -6785,8 +6785,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>
@@ -13204,8 +13204,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>

--- a/Client/Tables/G_VerInfoTable.xlsx
+++ b/Client/Tables/G_VerInfoTable.xlsx
@@ -140,7 +140,7 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -559,12 +559,24 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -585,7 +597,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>0.0</v>
@@ -597,7 +609,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>8</v>
@@ -622,7 +634,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>0.0</v>
@@ -634,7 +646,7 @@
         <v>0.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>8</v>
@@ -659,7 +671,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
         <v>0.0</v>
@@ -671,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -696,7 +708,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3">
         <v>0.0</v>
@@ -708,7 +720,7 @@
         <v>0.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>8</v>
@@ -730,43 +742,6 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
@@ -6978,12 +6953,24 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -7004,7 +6991,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>0.0</v>
@@ -7016,7 +7003,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>8</v>
@@ -7041,7 +7028,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>0.0</v>
@@ -7053,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>8</v>
@@ -7078,7 +7065,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
         <v>0.0</v>
@@ -7090,7 +7077,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -7115,7 +7102,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3">
         <v>0.0</v>
@@ -7127,7 +7114,7 @@
         <v>0.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>8</v>
@@ -7149,43 +7136,6 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
@@ -13397,12 +13347,24 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -13423,7 +13385,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>0.0</v>
@@ -13435,7 +13397,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>8</v>
@@ -13460,7 +13422,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>0.0</v>
@@ -13472,7 +13434,7 @@
         <v>0.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>8</v>
@@ -13497,7 +13459,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
         <v>0.0</v>
@@ -13509,7 +13471,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -13534,7 +13496,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3">
         <v>0.0</v>
@@ -13546,7 +13508,7 @@
         <v>0.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>8</v>
@@ -13568,43 +13530,6 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
